--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/TN WP 2026-27/SL 2.0/Virudhunagar.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/TN WP 2026-27/SL 2.0/Virudhunagar.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dex\Desktop\TN WP 2026-27\SL 2.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\TN WP 2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CF3E99-471C-48B1-B6BD-F677B418486F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE4B796-8CDE-4EAC-BD16-BB1793F90385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -746,10 +746,10 @@
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -757,12 +757,6 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -774,6 +768,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3424,47 +3424,47 @@
       <c r="B4" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48" t="s">
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="48"/>
-      <c r="H4" s="39" t="s">
+      <c r="G4" s="46"/>
+      <c r="H4" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="I4" s="40"/>
-      <c r="J4" s="48" t="s">
+      <c r="I4" s="48"/>
+      <c r="J4" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48" t="s">
+      <c r="K4" s="46"/>
+      <c r="L4" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="M4" s="48"/>
-      <c r="N4" s="39" t="s">
+      <c r="M4" s="46"/>
+      <c r="N4" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="O4" s="40"/>
+      <c r="O4" s="48"/>
       <c r="P4" s="49" t="s">
         <v>62</v>
       </c>
       <c r="Q4" s="49"/>
-      <c r="R4" s="48" t="s">
+      <c r="R4" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="S4" s="48"/>
+      <c r="S4" s="46"/>
       <c r="T4" s="50" t="s">
         <v>44</v>
       </c>
       <c r="U4" s="51"/>
-      <c r="V4" s="48" t="s">
+      <c r="V4" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="W4" s="48"/>
+      <c r="W4" s="46"/>
       <c r="X4" s="49" t="s">
         <v>63</v>
       </c>
@@ -3624,36 +3624,36 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="44"/>
-      <c r="V7" s="44"/>
-      <c r="W7" s="44"/>
-      <c r="X7" s="44"/>
-      <c r="Y7" s="44"/>
-      <c r="Z7" s="44"/>
-    </row>
-    <row r="8" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="40"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="40"/>
+      <c r="W7" s="40"/>
+      <c r="X7" s="40"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="40"/>
+    </row>
+    <row r="8" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>66</v>
       </c>
@@ -3689,7 +3689,7 @@
       <c r="Y8" s="11"/>
       <c r="Z8" s="11"/>
     </row>
-    <row r="9" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
         <v>67</v>
       </c>
@@ -3723,7 +3723,7 @@
       <c r="Y9" s="11"/>
       <c r="Z9" s="11"/>
     </row>
-    <row r="10" spans="1:26" ht="24.8" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A10" s="24" t="s">
         <v>68</v>
       </c>
@@ -3757,37 +3757,37 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="45" t="s">
+    <row r="11" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
+      <c r="A11" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46"/>
-      <c r="O11" s="46"/>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="46"/>
-      <c r="V11" s="46"/>
-      <c r="W11" s="46"/>
-      <c r="X11" s="46"/>
-      <c r="Y11" s="46"/>
-      <c r="Z11" s="46"/>
-    </row>
-    <row r="12" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="44"/>
+      <c r="X11" s="44"/>
+      <c r="Y11" s="44"/>
+      <c r="Z11" s="44"/>
+    </row>
+    <row r="12" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>72</v>
       </c>
@@ -3821,7 +3821,7 @@
       <c r="Y12" s="14"/>
       <c r="Z12" s="14"/>
     </row>
-    <row r="13" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
         <v>73</v>
       </c>
@@ -3857,7 +3857,7 @@
       <c r="Y13" s="16"/>
       <c r="Z13" s="16"/>
     </row>
-    <row r="14" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
         <v>74</v>
       </c>
@@ -3891,7 +3891,7 @@
       <c r="Y14" s="16"/>
       <c r="Z14" s="16"/>
     </row>
-    <row r="15" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
         <v>67</v>
       </c>
@@ -3927,7 +3927,7 @@
       <c r="Y15" s="16"/>
       <c r="Z15" s="16"/>
     </row>
-    <row r="16" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A16" s="24" t="s">
         <v>66</v>
       </c>
@@ -3961,7 +3961,7 @@
       <c r="Y16" s="16"/>
       <c r="Z16" s="16"/>
     </row>
-    <row r="17" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
         <v>75</v>
       </c>
@@ -3995,7 +3995,7 @@
       <c r="Y17" s="16"/>
       <c r="Z17" s="16"/>
     </row>
-    <row r="18" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>76</v>
       </c>
@@ -4029,7 +4029,7 @@
       <c r="Y18" s="16"/>
       <c r="Z18" s="16"/>
     </row>
-    <row r="19" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
         <v>66</v>
       </c>
@@ -4063,7 +4063,7 @@
       <c r="Y19" s="14"/>
       <c r="Z19" s="14"/>
     </row>
-    <row r="20" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
         <v>75</v>
       </c>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="Z20" s="14"/>
     </row>
-    <row r="21" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A21" s="24" t="s">
         <v>68</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>67</v>
       </c>
@@ -4171,7 +4171,7 @@
       <c r="Y22" s="16"/>
       <c r="Z22" s="16"/>
     </row>
-    <row r="23" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>67</v>
       </c>
@@ -4207,7 +4207,7 @@
       <c r="Y23" s="16"/>
       <c r="Z23" s="16"/>
     </row>
-    <row r="24" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>87</v>
       </c>
@@ -4243,7 +4243,7 @@
       <c r="Y24" s="38"/>
       <c r="Z24" s="16"/>
     </row>
-    <row r="25" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
         <v>88</v>
       </c>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="Z25" s="16"/>
     </row>
-    <row r="26" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>66</v>
       </c>
@@ -4311,7 +4311,7 @@
       <c r="Y26" s="14"/>
       <c r="Z26" s="14"/>
     </row>
-    <row r="27" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>88</v>
       </c>
@@ -4345,7 +4345,7 @@
       <c r="Y27" s="14"/>
       <c r="Z27" s="14"/>
     </row>
-    <row r="28" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>88</v>
       </c>
@@ -4379,7 +4379,7 @@
       <c r="Y28" s="14"/>
       <c r="Z28" s="14"/>
     </row>
-    <row r="29" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>74</v>
       </c>
@@ -4413,7 +4413,7 @@
       <c r="Y29" s="14"/>
       <c r="Z29" s="14"/>
     </row>
-    <row r="30" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A30" s="33" t="s">
         <v>72</v>
       </c>
@@ -4447,7 +4447,7 @@
       <c r="Y30" s="14"/>
       <c r="Z30" s="14"/>
     </row>
-    <row r="31" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>88</v>
       </c>
@@ -4481,7 +4481,7 @@
       <c r="Y31" s="14"/>
       <c r="Z31" s="14"/>
     </row>
-    <row r="32" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A32" s="33" t="s">
         <v>97</v>
       </c>
@@ -4515,7 +4515,7 @@
       <c r="Y32" s="14"/>
       <c r="Z32" s="14"/>
     </row>
-    <row r="33" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
         <v>97</v>
       </c>
@@ -4549,7 +4549,7 @@
       <c r="Y33" s="14"/>
       <c r="Z33" s="14"/>
     </row>
-    <row r="34" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A34" s="33" t="s">
         <v>66</v>
       </c>
@@ -4583,7 +4583,7 @@
       <c r="Y34" s="14"/>
       <c r="Z34" s="14"/>
     </row>
-    <row r="35" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A35" s="33" t="s">
         <v>72</v>
       </c>
@@ -4617,7 +4617,7 @@
       <c r="Y35" s="14"/>
       <c r="Z35" s="14"/>
     </row>
-    <row r="36" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A36" s="33" t="s">
         <v>97</v>
       </c>
@@ -4651,7 +4651,7 @@
       <c r="Y36" s="14"/>
       <c r="Z36" s="14"/>
     </row>
-    <row r="37" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A37" s="33" t="s">
         <v>73</v>
       </c>
@@ -4685,7 +4685,7 @@
       <c r="Y37" s="14"/>
       <c r="Z37" s="14"/>
     </row>
-    <row r="38" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:26" ht="14.3" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
       <c r="B38" s="23" t="s">
         <v>29</v>
@@ -4716,32 +4716,32 @@
       <c r="Z38" s="26"/>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A39" s="47"/>
-      <c r="B39" s="47"/>
-      <c r="C39" s="47"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="47"/>
-      <c r="I39" s="47"/>
-      <c r="J39" s="47"/>
-      <c r="K39" s="47"/>
-      <c r="L39" s="47"/>
-      <c r="M39" s="47"/>
-      <c r="N39" s="47"/>
-      <c r="O39" s="47"/>
-      <c r="P39" s="47"/>
-      <c r="Q39" s="47"/>
-      <c r="R39" s="47"/>
-      <c r="S39" s="47"/>
-      <c r="T39" s="47"/>
-      <c r="U39" s="47"/>
-      <c r="V39" s="47"/>
-      <c r="W39" s="47"/>
-      <c r="X39" s="47"/>
-      <c r="Y39" s="47"/>
-      <c r="Z39" s="47"/>
+      <c r="A39" s="45"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="45"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="45"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="45"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="45"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="45"/>
+      <c r="O39" s="45"/>
+      <c r="P39" s="45"/>
+      <c r="Q39" s="45"/>
+      <c r="R39" s="45"/>
+      <c r="S39" s="45"/>
+      <c r="T39" s="45"/>
+      <c r="U39" s="45"/>
+      <c r="V39" s="45"/>
+      <c r="W39" s="45"/>
+      <c r="X39" s="45"/>
+      <c r="Y39" s="45"/>
+      <c r="Z39" s="45"/>
     </row>
     <row r="40" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A40" s="20" t="s">
@@ -4760,6 +4760,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A2:Z2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:Q3"/>
+    <mergeCell ref="U3:Z3"/>
     <mergeCell ref="A7:Z7"/>
     <mergeCell ref="A11:Z11"/>
     <mergeCell ref="A39:Z39"/>
@@ -4776,12 +4782,6 @@
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A2:Z2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:Q3"/>
-    <mergeCell ref="U3:Z3"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
@@ -6427,47 +6427,47 @@
       <c r="B4" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48" t="s">
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="48"/>
-      <c r="H4" s="39" t="s">
+      <c r="G4" s="46"/>
+      <c r="H4" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="I4" s="40"/>
-      <c r="J4" s="48" t="s">
+      <c r="I4" s="48"/>
+      <c r="J4" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48" t="s">
+      <c r="K4" s="46"/>
+      <c r="L4" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="M4" s="48"/>
-      <c r="N4" s="39" t="s">
+      <c r="M4" s="46"/>
+      <c r="N4" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="O4" s="40"/>
+      <c r="O4" s="48"/>
       <c r="P4" s="49" t="s">
         <v>62</v>
       </c>
       <c r="Q4" s="49"/>
-      <c r="R4" s="48" t="s">
+      <c r="R4" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="S4" s="48"/>
+      <c r="S4" s="46"/>
       <c r="T4" s="50" t="s">
         <v>44</v>
       </c>
       <c r="U4" s="51"/>
-      <c r="V4" s="48" t="s">
+      <c r="V4" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="W4" s="48"/>
+      <c r="W4" s="46"/>
       <c r="X4" s="49" t="s">
         <v>63</v>
       </c>
@@ -6627,36 +6627,36 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="44"/>
-      <c r="V7" s="44"/>
-      <c r="W7" s="44"/>
-      <c r="X7" s="44"/>
-      <c r="Y7" s="44"/>
-      <c r="Z7" s="44"/>
-    </row>
-    <row r="8" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="40"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="40"/>
+      <c r="W7" s="40"/>
+      <c r="X7" s="40"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="40"/>
+    </row>
+    <row r="8" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>72</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
         <v>75</v>
       </c>
@@ -6730,7 +6730,7 @@
       <c r="Y9" s="11"/>
       <c r="Z9" s="11"/>
     </row>
-    <row r="10" spans="1:26" ht="24.8" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A10" s="24" t="s">
         <v>75</v>
       </c>
@@ -6768,37 +6768,37 @@
       <c r="Y10" s="11"/>
       <c r="Z10" s="11"/>
     </row>
-    <row r="11" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="45" t="s">
+    <row r="11" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
+      <c r="A11" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46"/>
-      <c r="O11" s="46"/>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="46"/>
-      <c r="V11" s="46"/>
-      <c r="W11" s="46"/>
-      <c r="X11" s="46"/>
-      <c r="Y11" s="46"/>
-      <c r="Z11" s="46"/>
-    </row>
-    <row r="12" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="44"/>
+      <c r="X11" s="44"/>
+      <c r="Y11" s="44"/>
+      <c r="Z11" s="44"/>
+    </row>
+    <row r="12" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
         <v>73</v>
       </c>
@@ -6832,7 +6832,7 @@
       <c r="Y12" s="14"/>
       <c r="Z12" s="14"/>
     </row>
-    <row r="13" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
         <v>66</v>
       </c>
@@ -6866,7 +6866,7 @@
       <c r="Y13" s="16"/>
       <c r="Z13" s="16"/>
     </row>
-    <row r="14" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
         <v>76</v>
       </c>
@@ -6900,7 +6900,7 @@
       <c r="Y14" s="16"/>
       <c r="Z14" s="16"/>
     </row>
-    <row r="15" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
         <v>74</v>
       </c>
@@ -6934,7 +6934,7 @@
       <c r="Y15" s="16"/>
       <c r="Z15" s="16"/>
     </row>
-    <row r="16" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
         <v>97</v>
       </c>
@@ -6968,7 +6968,7 @@
       <c r="Y16" s="16"/>
       <c r="Z16" s="16"/>
     </row>
-    <row r="17" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
         <v>88</v>
       </c>
@@ -7002,7 +7002,7 @@
       <c r="Y17" s="16"/>
       <c r="Z17" s="16"/>
     </row>
-    <row r="18" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A18" s="24" t="s">
         <v>68</v>
       </c>
@@ -7036,7 +7036,7 @@
       <c r="Y18" s="16"/>
       <c r="Z18" s="16"/>
     </row>
-    <row r="19" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A19" s="33" t="s">
         <v>72</v>
       </c>
@@ -7070,7 +7070,7 @@
       <c r="Y19" s="16"/>
       <c r="Z19" s="16"/>
     </row>
-    <row r="20" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A20" s="24" t="s">
         <v>66</v>
       </c>
@@ -7106,7 +7106,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="13.6" x14ac:dyDescent="0.25">
       <c r="A21" s="33" t="s">
         <v>97</v>
       </c>
@@ -7140,7 +7140,7 @@
       <c r="Y21" s="14"/>
       <c r="Z21" s="14"/>
     </row>
-    <row r="22" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:26" ht="14.3" x14ac:dyDescent="0.2">
       <c r="A22" s="13"/>
       <c r="B22" s="23" t="s">
         <v>29</v>
@@ -7171,32 +7171,32 @@
       <c r="Z22" s="26"/>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A23" s="47"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47"/>
-      <c r="O23" s="47"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47"/>
-      <c r="S23" s="47"/>
-      <c r="T23" s="47"/>
-      <c r="U23" s="47"/>
-      <c r="V23" s="47"/>
-      <c r="W23" s="47"/>
-      <c r="X23" s="47"/>
-      <c r="Y23" s="47"/>
-      <c r="Z23" s="47"/>
+      <c r="A23" s="45"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="45"/>
+      <c r="R23" s="45"/>
+      <c r="S23" s="45"/>
+      <c r="T23" s="45"/>
+      <c r="U23" s="45"/>
+      <c r="V23" s="45"/>
+      <c r="W23" s="45"/>
+      <c r="X23" s="45"/>
+      <c r="Y23" s="45"/>
+      <c r="Z23" s="45"/>
     </row>
     <row r="24" spans="1:26" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A24" s="20" t="s">
@@ -7215,12 +7215,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A7:Z7"/>
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A2:Z2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:Q3"/>
-    <mergeCell ref="U3:Z3"/>
     <mergeCell ref="A11:Z11"/>
     <mergeCell ref="A23:Z23"/>
     <mergeCell ref="J4:K4"/>
@@ -7237,6 +7231,12 @@
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="X4:Y4"/>
     <mergeCell ref="Z4:Z5"/>
+    <mergeCell ref="A7:Z7"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A2:Z2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:Q3"/>
+    <mergeCell ref="U3:Z3"/>
   </mergeCells>
   <pageMargins left="0.1875" right="0.31496062992125984" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
